--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260714.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260714.xlsx
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>780,000</t>
+          <t>1,240,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,240,000</t>
+          <t>780,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
